--- a/example_data/validation_results.xlsx
+++ b/example_data/validation_results.xlsx
@@ -525,10 +525,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>90.90909090909091</v>
+        <v>95.45454545454545</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
         <v>100</v>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>82.35294117647058</v>
+        <v>73.68421052631578</v>
       </c>
     </row>
   </sheetData>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,18 +633,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.science.org/doi/10.1126/science.adt3971</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Karl Deisseroth</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/example_data/validation_results.xlsx
+++ b/example_data/validation_results.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Authors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,10 +524,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>95.45454545454545</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
         <v>100</v>
@@ -550,30 +549,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>First Author Role Correct</t>
+          <t>Ambiguous Email Assignments</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>8.695652173913043</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Last Author Role Correct</t>
+          <t>First Author Role Correct</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>100</v>
@@ -582,55 +581,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Last Author Role Correct</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Corresponding Author Role Correct</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>19</v>
-      </c>
-      <c r="C10" t="n">
-        <v>14</v>
-      </c>
-      <c r="D10" t="n">
-        <v>73.68421052631578</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>author_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.science.org/doi/10.1126/science.adt3971</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Carolyn I. Rodríguez</t>
-        </is>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
